--- a/docs/i18n/translations.xlsx
+++ b/docs/i18n/translations.xlsx
@@ -73,7 +73,7 @@
     <t>• Page copy — 374 rows from the website pages.</t>
   </si>
   <si>
-    <t>• Interface — 159 rows of buttons, labels, form text and messages.</t>
+    <t>• Interface — 165 rows of buttons, labels, form text and messages.</t>
   </si>
   <si>
     <t>• Glossary — terms to keep or translate consistently.</t>
@@ -3862,6 +3862,15 @@
     <t>U-014</t>
   </si>
   <si>
+    <t>messages:nav.home</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>U-015</t>
+  </si>
+  <si>
     <t>messages:nav.solutions
 messages:footer.solutions</t>
   </si>
@@ -3869,13 +3878,13 @@
     <t>Solutions</t>
   </si>
   <si>
-    <t>U-015</t>
+    <t>U-016</t>
   </si>
   <si>
     <t>messages:nav.products</t>
   </si>
   <si>
-    <t>U-016</t>
+    <t>U-017</t>
   </si>
   <si>
     <t>messages:nav.industries
@@ -3886,7 +3895,7 @@
     <t>Industries</t>
   </si>
   <si>
-    <t>U-017</t>
+    <t>U-018</t>
   </si>
   <si>
     <t>messages:nav.services</t>
@@ -3895,7 +3904,7 @@
     <t>Services</t>
   </si>
   <si>
-    <t>U-018</t>
+    <t>U-019</t>
   </si>
   <si>
     <t>messages:nav.projects
@@ -3905,7 +3914,7 @@
     <t>Projects</t>
   </si>
   <si>
-    <t>U-019</t>
+    <t>U-020</t>
   </si>
   <si>
     <t>messages:nav.about</t>
@@ -3914,13 +3923,13 @@
     <t>About</t>
   </si>
   <si>
-    <t>U-020</t>
+    <t>U-021</t>
   </si>
   <si>
     <t>messages:nav.contact</t>
   </si>
   <si>
-    <t>U-021</t>
+    <t>U-022</t>
   </si>
   <si>
     <t>messages:nav.featured</t>
@@ -3929,7 +3938,7 @@
     <t>Featured capability</t>
   </si>
   <si>
-    <t>U-022</t>
+    <t>U-023</t>
   </si>
   <si>
     <t>messages:nav.allSolutions</t>
@@ -3938,7 +3947,7 @@
     <t>All solutions</t>
   </si>
   <si>
-    <t>U-023</t>
+    <t>U-024</t>
   </si>
   <si>
     <t>messages:nav.howWeWork</t>
@@ -3947,7 +3956,7 @@
     <t>How we work</t>
   </si>
   <si>
-    <t>U-024</t>
+    <t>U-025</t>
   </si>
   <si>
     <t>messages:nav.allIndustries</t>
@@ -3956,7 +3965,7 @@
     <t>All industries</t>
   </si>
   <si>
-    <t>U-025</t>
+    <t>U-026</t>
   </si>
   <si>
     <t>messages:nav.allServices</t>
@@ -3965,7 +3974,7 @@
     <t>All services</t>
   </si>
   <si>
-    <t>U-026</t>
+    <t>U-027</t>
   </si>
   <si>
     <t>messages:nav.ourApproach</t>
@@ -3974,7 +3983,7 @@
     <t>Our approach</t>
   </si>
   <si>
-    <t>U-027</t>
+    <t>U-028</t>
   </si>
   <si>
     <t>messages:nav.askProducts</t>
@@ -3983,7 +3992,7 @@
     <t>Ask about products</t>
   </si>
   <si>
-    <t>U-028</t>
+    <t>U-029</t>
   </si>
   <si>
     <t>messages:nav.productsIntro</t>
@@ -3992,7 +4001,7 @@
     <t>Technology categories we supply and integrate.</t>
   </si>
   <si>
-    <t>U-029</t>
+    <t>U-030</t>
   </si>
   <si>
     <t>messages:nav.aboutLinks.whoWeAre</t>
@@ -4001,7 +4010,7 @@
     <t>Who we are</t>
   </si>
   <si>
-    <t>U-030</t>
+    <t>U-031</t>
   </si>
   <si>
     <t>messages:nav.aboutLinks.journey</t>
@@ -4010,7 +4019,7 @@
     <t>Our journey</t>
   </si>
   <si>
-    <t>U-031</t>
+    <t>U-032</t>
   </si>
   <si>
     <t>messages:nav.aboutLinks.visionMission</t>
@@ -4019,7 +4028,7 @@
     <t>Vision &amp; mission</t>
   </si>
   <si>
-    <t>U-032</t>
+    <t>U-033</t>
   </si>
   <si>
     <t>messages:nav.aboutLinks.values</t>
@@ -4028,7 +4037,7 @@
     <t>Core values</t>
   </si>
   <si>
-    <t>U-033</t>
+    <t>U-034</t>
   </si>
   <si>
     <t>messages:nav.aboutLinks.why</t>
@@ -4037,7 +4046,7 @@
     <t>Why Vision Plus</t>
   </si>
   <si>
-    <t>U-034</t>
+    <t>U-035</t>
   </si>
   <si>
     <t>messages:nav.aboutLinks.partners
@@ -4047,7 +4056,7 @@
     <t>Technology partners</t>
   </si>
   <si>
-    <t>U-035</t>
+    <t>U-036</t>
   </si>
   <si>
     <t>messages:nav.aboutLinks.companyProfile</t>
@@ -4056,7 +4065,7 @@
     <t>Company profile</t>
   </si>
   <si>
-    <t>U-036</t>
+    <t>U-037</t>
   </si>
   <si>
     <t>messages:cta.consultation
@@ -4066,7 +4075,7 @@
     <t>Request a consultation</t>
   </si>
   <si>
-    <t>U-037</t>
+    <t>U-038</t>
   </si>
   <si>
     <t>messages:cta.exploreSolutions</t>
@@ -4075,7 +4084,7 @@
     <t>Explore solutions</t>
   </si>
   <si>
-    <t>U-038</t>
+    <t>U-039</t>
   </si>
   <si>
     <t>messages:cta.exploreMnvr</t>
@@ -4084,7 +4093,7 @@
     <t>Explore Mobile NVR</t>
   </si>
   <si>
-    <t>U-039</t>
+    <t>U-040</t>
   </si>
   <si>
     <t>messages:cta.allIndustries</t>
@@ -4093,7 +4102,7 @@
     <t>Explore industries</t>
   </si>
   <si>
-    <t>U-040</t>
+    <t>U-041</t>
   </si>
   <si>
     <t>messages:cta.approach</t>
@@ -4102,7 +4111,7 @@
     <t>See how we work</t>
   </si>
   <si>
-    <t>U-041</t>
+    <t>U-042</t>
   </si>
   <si>
     <t>messages:cta.ourStory</t>
@@ -4111,7 +4120,7 @@
     <t>Our story</t>
   </si>
   <si>
-    <t>U-042</t>
+    <t>U-043</t>
   </si>
   <si>
     <t>messages:cta.viewProjects</t>
@@ -4120,7 +4129,7 @@
     <t>View projects</t>
   </si>
   <si>
-    <t>U-043</t>
+    <t>U-044</t>
   </si>
   <si>
     <t>messages:cta.companyProfile</t>
@@ -4129,7 +4138,7 @@
     <t>View company profile</t>
   </si>
   <si>
-    <t>U-044</t>
+    <t>U-045</t>
   </si>
   <si>
     <t>messages:cta.learnMore</t>
@@ -4138,7 +4147,7 @@
     <t>Learn more</t>
   </si>
   <si>
-    <t>U-045</t>
+    <t>U-046</t>
   </si>
   <si>
     <t>messages:home.capabilitiesLabel
@@ -4148,7 +4157,7 @@
     <t>Capabilities</t>
   </si>
   <si>
-    <t>U-046</t>
+    <t>U-047</t>
   </si>
   <si>
     <t>messages:home.marketsLabel</t>
@@ -4157,7 +4166,7 @@
     <t>Markets</t>
   </si>
   <si>
-    <t>U-047</t>
+    <t>U-048</t>
   </si>
   <si>
     <t>messages:home.step</t>
@@ -4169,7 +4178,7 @@
     <t>Keep {placeholders} exactly; complete every plural form your language needs (Arabic: zero/one/two/few/many/other). Short UI or heading text: keep within the hint so the layout holds</t>
   </si>
   <si>
-    <t>U-048</t>
+    <t>U-049</t>
   </si>
   <si>
     <t>messages:footer.company</t>
@@ -4178,7 +4187,7 @@
     <t>Company</t>
   </si>
   <si>
-    <t>U-049</t>
+    <t>U-050</t>
   </si>
   <si>
     <t>messages:footer.offices</t>
@@ -4187,7 +4196,7 @@
     <t>Offices</t>
   </si>
   <si>
-    <t>U-050</t>
+    <t>U-051</t>
   </si>
   <si>
     <t>messages:footer.rights</t>
@@ -4199,7 +4208,7 @@
     <t>Keep {placeholders} exactly; complete every plural form your language needs (Arabic: zero/one/two/few/many/other). Keep “VISION PLUS” in Latin capitals (Q-07). Short UI or heading text: keep within the hint so the layout holds</t>
   </si>
   <si>
-    <t>U-051</t>
+    <t>U-052</t>
   </si>
   <si>
     <t>messages:footer.privacy</t>
@@ -4208,7 +4217,7 @@
     <t>Privacy policy</t>
   </si>
   <si>
-    <t>U-052</t>
+    <t>U-053</t>
   </si>
   <si>
     <t>messages:placeholder.address</t>
@@ -4217,7 +4226,7 @@
     <t>Office address — pending client</t>
   </si>
   <si>
-    <t>U-053</t>
+    <t>U-054</t>
   </si>
   <si>
     <t>messages:placeholder.phone</t>
@@ -4226,7 +4235,7 @@
     <t>Phone — pending client</t>
   </si>
   <si>
-    <t>U-054</t>
+    <t>U-055</t>
   </si>
   <si>
     <t>messages:placeholder.email</t>
@@ -4235,7 +4244,7 @@
     <t>Email — pending client</t>
   </si>
   <si>
-    <t>U-055</t>
+    <t>U-056</t>
   </si>
   <si>
     <t>messages:placeholder.projectPending</t>
@@ -4244,7 +4253,7 @@
     <t>Awaiting client project data</t>
   </si>
   <si>
-    <t>U-056</t>
+    <t>U-057</t>
   </si>
   <si>
     <t>messages:placeholder.projectNote</t>
@@ -4253,7 +4262,7 @@
     <t>Projects are published only with real data and client permission.</t>
   </si>
   <si>
-    <t>U-057</t>
+    <t>U-058</t>
   </si>
   <si>
     <t>messages:placeholder.partnerPending</t>
@@ -4262,7 +4271,7 @@
     <t>Partner logo</t>
   </si>
   <si>
-    <t>U-058</t>
+    <t>U-059</t>
   </si>
   <si>
     <t>messages:placeholder.partnerNote</t>
@@ -4271,7 +4280,52 @@
     <t>Partner logos appear once confirmed by Vision Plus.</t>
   </si>
   <si>
-    <t>U-059</t>
+    <t>U-060</t>
+  </si>
+  <si>
+    <t>messages:preview.labIntro</t>
+  </si>
+  <si>
+    <t>Live design system for review (preview only, never published).</t>
+  </si>
+  <si>
+    <t>U-061</t>
+  </si>
+  <si>
+    <t>messages:preview.labTitle</t>
+  </si>
+  <si>
+    <t>Style guide</t>
+  </si>
+  <si>
+    <t>U-062</t>
+  </si>
+  <si>
+    <t>messages:preview.sceneFirstCut</t>
+  </si>
+  <si>
+    <t>Route scene, first cut for direction review: the storyboard is awaiting client approval (D-20).</t>
+  </si>
+  <si>
+    <t>U-063</t>
+  </si>
+  <si>
+    <t>messages:preview.sectionPending</t>
+  </si>
+  <si>
+    <t>Section content: Phase 5</t>
+  </si>
+  <si>
+    <t>U-064</t>
+  </si>
+  <si>
+    <t>messages:preview.templatePending</t>
+  </si>
+  <si>
+    <t>Page template: the full page is built in Phase 5. It is shown here so that navigation works in preview.</t>
+  </si>
+  <si>
+    <t>U-065</t>
   </si>
   <si>
     <t>messages:preview.label</t>
@@ -4280,7 +4334,7 @@
     <t>Preview</t>
   </si>
   <si>
-    <t>U-060</t>
+    <t>U-066</t>
   </si>
   <si>
     <t>messages:preview.title</t>
@@ -4289,7 +4343,7 @@
     <t>Preview build — not for publication</t>
   </si>
   <si>
-    <t>U-061</t>
+    <t>U-067</t>
   </si>
   <si>
     <t>messages:preview.copyStatus</t>
@@ -4298,7 +4352,7 @@
     <t>Copy: {status}</t>
   </si>
   <si>
-    <t>U-062</t>
+    <t>U-068</t>
   </si>
   <si>
     <t>messages:preview.statusApproved</t>
@@ -4307,7 +4361,7 @@
     <t>approved English</t>
   </si>
   <si>
-    <t>U-063</t>
+    <t>U-069</t>
   </si>
   <si>
     <t>messages:preview.statusDraftMt</t>
@@ -4316,7 +4370,7 @@
     <t>draft translation for layout review (not approved)</t>
   </si>
   <si>
-    <t>U-064</t>
+    <t>U-070</t>
   </si>
   <si>
     <t>messages:preview.logo</t>
@@ -4325,7 +4379,7 @@
     <t>Interim wordmark — official logo pending</t>
   </si>
   <si>
-    <t>U-065</t>
+    <t>U-071</t>
   </si>
   <si>
     <t>messages:preview.images</t>
@@ -4334,7 +4388,7 @@
     <t>Image slots show placeholders until real photography is delivered</t>
   </si>
   <si>
-    <t>U-066</t>
+    <t>U-072</t>
   </si>
   <si>
     <t>messages:preview.sections</t>
@@ -4343,7 +4397,7 @@
     <t>Projects and Partners are hidden in production until real data exists</t>
   </si>
   <si>
-    <t>U-067</t>
+    <t>U-073</t>
   </si>
   <si>
     <t>messages:preview.close</t>
@@ -4352,7 +4406,7 @@
     <t>Close</t>
   </si>
   <si>
-    <t>U-068</t>
+    <t>U-074</t>
   </si>
   <si>
     <t>messages:solution.lifecycleTitle</t>
@@ -4361,7 +4415,7 @@
     <t>Delivered through our lifecycle</t>
   </si>
   <si>
-    <t>U-069</t>
+    <t>U-075</t>
   </si>
   <si>
     <t>messages:solution.related</t>
@@ -4370,7 +4424,7 @@
     <t>Related</t>
   </si>
   <si>
-    <t>U-070</t>
+    <t>U-076</t>
   </si>
   <si>
     <t>messages:solution.relatedCategories</t>
@@ -4379,7 +4433,7 @@
     <t>Product categories</t>
   </si>
   <si>
-    <t>U-071</t>
+    <t>U-077</t>
   </si>
   <si>
     <t>messages:solution.otherSolutions</t>
@@ -4388,7 +4442,7 @@
     <t>Other solutions</t>
   </si>
   <si>
-    <t>U-072</t>
+    <t>U-078</t>
   </si>
   <si>
     <t>messages:solution.acrossEnvironments</t>
@@ -4397,7 +4451,7 @@
     <t>Applies across environments</t>
   </si>
   <si>
-    <t>U-073</t>
+    <t>U-079</t>
   </si>
   <si>
     <t>messages:solution.ctaTitle</t>
@@ -4406,7 +4460,7 @@
     <t>Discuss your {solution} requirements.</t>
   </si>
   <si>
-    <t>U-074</t>
+    <t>U-080</t>
   </si>
   <si>
     <t>messages:scene.stepsLabel</t>
@@ -4415,7 +4469,7 @@
     <t>{name}: steps</t>
   </si>
   <si>
-    <t>U-075</t>
+    <t>U-081</t>
   </si>
   <si>
     <t>messages:scene.progress</t>
@@ -4424,7 +4478,7 @@
     <t>Step {current} of {total}</t>
   </si>
   <si>
-    <t>U-076</t>
+    <t>U-082</t>
   </si>
   <si>
     <t>messages:scene.skip</t>
@@ -4433,7 +4487,7 @@
     <t>Skip to the next section</t>
   </si>
   <si>
-    <t>U-077</t>
+    <t>U-083</t>
   </si>
   <si>
     <t>messages:industries.relatedSolutions</t>
@@ -4442,7 +4496,7 @@
     <t>Related solutions</t>
   </si>
   <si>
-    <t>U-078</t>
+    <t>U-084</t>
   </si>
   <si>
     <t>messages:industries.relatedProjects</t>
@@ -4451,7 +4505,7 @@
     <t>Related projects</t>
   </si>
   <si>
-    <t>U-079</t>
+    <t>U-085</t>
   </si>
   <si>
     <t>messages:services.stages</t>
@@ -4460,7 +4514,7 @@
     <t>Stages:</t>
   </si>
   <si>
-    <t>U-080</t>
+    <t>U-086</t>
   </si>
   <si>
     <t>messages:products.askCategory</t>
@@ -4469,7 +4523,7 @@
     <t>Ask about this category</t>
   </si>
   <si>
-    <t>U-081</t>
+    <t>U-087</t>
   </si>
   <si>
     <t>messages:products.relatedSolution</t>
@@ -4478,7 +4532,7 @@
     <t>Related solution</t>
   </si>
   <si>
-    <t>U-082</t>
+    <t>U-088</t>
   </si>
   <si>
     <t>messages:products.brands</t>
@@ -4487,7 +4541,7 @@
     <t>Brands we supply</t>
   </si>
   <si>
-    <t>U-083</t>
+    <t>U-089</t>
   </si>
   <si>
     <t>messages:projects.filters.label</t>
@@ -4496,7 +4550,7 @@
     <t>Filter projects</t>
   </si>
   <si>
-    <t>U-084</t>
+    <t>U-090</t>
   </si>
   <si>
     <t>messages:projects.filters.sector</t>
@@ -4505,7 +4559,7 @@
     <t>Sector</t>
   </si>
   <si>
-    <t>U-085</t>
+    <t>U-091</t>
   </si>
   <si>
     <t>messages:projects.filters.solution</t>
@@ -4514,7 +4568,7 @@
     <t>Solution</t>
   </si>
   <si>
-    <t>U-086</t>
+    <t>U-092</t>
   </si>
   <si>
     <t>messages:projects.filters.country</t>
@@ -4523,7 +4577,7 @@
     <t>Country</t>
   </si>
   <si>
-    <t>U-087</t>
+    <t>U-093</t>
   </si>
   <si>
     <t>messages:projects.filters.all</t>
@@ -4532,7 +4586,7 @@
     <t>All</t>
   </si>
   <si>
-    <t>U-088</t>
+    <t>U-094</t>
   </si>
   <si>
     <t>messages:projects.filters.reset</t>
@@ -4541,7 +4595,7 @@
     <t>Reset filters</t>
   </si>
   <si>
-    <t>U-089</t>
+    <t>U-095</t>
   </si>
   <si>
     <t>messages:projects.count</t>
@@ -4550,7 +4604,7 @@
     <t>{count, plural, one {# project} other {# projects}}</t>
   </si>
   <si>
-    <t>U-090</t>
+    <t>U-096</t>
   </si>
   <si>
     <t>messages:projects.empty.title</t>
@@ -4559,7 +4613,7 @@
     <t>No projects match these filters.</t>
   </si>
   <si>
-    <t>U-091</t>
+    <t>U-097</t>
   </si>
   <si>
     <t>messages:projects.empty.action</t>
@@ -4568,7 +4622,7 @@
     <t>Show all projects</t>
   </si>
   <si>
-    <t>U-092</t>
+    <t>U-098</t>
   </si>
   <si>
     <t>messages:projects.facts</t>
@@ -4577,7 +4631,7 @@
     <t>Project facts</t>
   </si>
   <si>
-    <t>U-093</t>
+    <t>U-099</t>
   </si>
   <si>
     <t>messages:projects.gallery.label</t>
@@ -4586,7 +4640,7 @@
     <t>Project gallery</t>
   </si>
   <si>
-    <t>U-094</t>
+    <t>U-100</t>
   </si>
   <si>
     <t>messages:projects.gallery.open</t>
@@ -4595,7 +4649,7 @@
     <t>Open image {n} of {total}</t>
   </si>
   <si>
-    <t>U-095</t>
+    <t>U-101</t>
   </si>
   <si>
     <t>messages:projects.gallery.previous</t>
@@ -4604,7 +4658,7 @@
     <t>Previous image</t>
   </si>
   <si>
-    <t>U-096</t>
+    <t>U-102</t>
   </si>
   <si>
     <t>messages:projects.gallery.next</t>
@@ -4613,7 +4667,7 @@
     <t>Next image</t>
   </si>
   <si>
-    <t>U-097</t>
+    <t>U-103</t>
   </si>
   <si>
     <t>messages:projects.gallery.close</t>
@@ -4622,7 +4676,7 @@
     <t>Close gallery</t>
   </si>
   <si>
-    <t>U-098</t>
+    <t>U-104</t>
   </si>
   <si>
     <t>messages:projects.nextProject</t>
@@ -4631,7 +4685,7 @@
     <t>Next project</t>
   </si>
   <si>
-    <t>U-099</t>
+    <t>U-105</t>
   </si>
   <si>
     <t>messages:about.onThisPage</t>
@@ -4640,7 +4694,7 @@
     <t>On this page</t>
   </si>
   <si>
-    <t>U-100</t>
+    <t>U-106</t>
   </si>
   <si>
     <t>messages:form.title</t>
@@ -4649,7 +4703,7 @@
     <t>Send an inquiry</t>
   </si>
   <si>
-    <t>U-101</t>
+    <t>U-107</t>
   </si>
   <si>
     <t>messages:form.type.label</t>
@@ -4658,7 +4712,7 @@
     <t>Inquiry type</t>
   </si>
   <si>
-    <t>U-102</t>
+    <t>U-108</t>
   </si>
   <si>
     <t>messages:form.type.product</t>
@@ -4667,7 +4721,7 @@
     <t>Product inquiry</t>
   </si>
   <si>
-    <t>U-103</t>
+    <t>U-109</t>
   </si>
   <si>
     <t>messages:form.type.general</t>
@@ -4676,7 +4730,7 @@
     <t>General inquiry</t>
   </si>
   <si>
-    <t>U-104</t>
+    <t>U-110</t>
   </si>
   <si>
     <t>messages:form.type.partnership</t>
@@ -4685,7 +4739,7 @@
     <t>Become a partner</t>
   </si>
   <si>
-    <t>U-105</t>
+    <t>U-111</t>
   </si>
   <si>
     <t>messages:form.name.label</t>
@@ -4694,7 +4748,7 @@
     <t>Full name</t>
   </si>
   <si>
-    <t>U-106</t>
+    <t>U-112</t>
   </si>
   <si>
     <t>messages:form.company.label</t>
@@ -4703,7 +4757,7 @@
     <t>Company / organization</t>
   </si>
   <si>
-    <t>U-107</t>
+    <t>U-113</t>
   </si>
   <si>
     <t>messages:form.email.label
@@ -4713,7 +4767,7 @@
     <t>Email</t>
   </si>
   <si>
-    <t>U-108</t>
+    <t>U-114</t>
   </si>
   <si>
     <t>messages:form.phone.label
@@ -4723,7 +4777,7 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>U-109</t>
+    <t>U-115</t>
   </si>
   <si>
     <t>messages:form.phone.hint</t>
@@ -4732,7 +4786,7 @@
     <t>Include the country code, for example +974.</t>
   </si>
   <si>
-    <t>U-110</t>
+    <t>U-116</t>
   </si>
   <si>
     <t>messages:form.location.label</t>
@@ -4741,19 +4795,19 @@
     <t>Project location</t>
   </si>
   <si>
-    <t>U-111</t>
+    <t>U-117</t>
   </si>
   <si>
     <t>messages:form.location.qatar</t>
   </si>
   <si>
-    <t>U-112</t>
+    <t>U-118</t>
   </si>
   <si>
     <t>messages:form.location.egypt</t>
   </si>
   <si>
-    <t>U-113</t>
+    <t>U-119</t>
   </si>
   <si>
     <t>messages:form.location.other
@@ -4763,7 +4817,7 @@
     <t>Other</t>
   </si>
   <si>
-    <t>U-114</t>
+    <t>U-120</t>
   </si>
   <si>
     <t>messages:form.industry.label</t>
@@ -4772,7 +4826,7 @@
     <t>Industry</t>
   </si>
   <si>
-    <t>U-115</t>
+    <t>U-121</t>
   </si>
   <si>
     <t>messages:form.solution.label</t>
@@ -4781,7 +4835,7 @@
     <t>Solution of interest</t>
   </si>
   <si>
-    <t>U-116</t>
+    <t>U-122</t>
   </si>
   <si>
     <t>messages:form.solution.services</t>
@@ -4790,7 +4844,7 @@
     <t>Professional services</t>
   </si>
   <si>
-    <t>U-117</t>
+    <t>U-123</t>
   </si>
   <si>
     <t>messages:form.solution.notSure</t>
@@ -4799,7 +4853,7 @@
     <t>Not sure yet</t>
   </si>
   <si>
-    <t>U-118</t>
+    <t>U-124</t>
   </si>
   <si>
     <t>messages:form.category.label</t>
@@ -4808,7 +4862,7 @@
     <t>Product category</t>
   </si>
   <si>
-    <t>U-119</t>
+    <t>U-125</t>
   </si>
   <si>
     <t>messages:form.message.label</t>
@@ -4817,7 +4871,7 @@
     <t>Message</t>
   </si>
   <si>
-    <t>U-120</t>
+    <t>U-126</t>
   </si>
   <si>
     <t>messages:form.message.hint</t>
@@ -4826,7 +4880,7 @@
     <t>Tell us about the site, the requirement and any timeline.</t>
   </si>
   <si>
-    <t>U-121</t>
+    <t>U-127</t>
   </si>
   <si>
     <t>messages:form.consent.label</t>
@@ -4838,7 +4892,7 @@
     <t>Keep the &lt;tags&gt; around the linked words. Keep “VISION PLUS” in Latin capitals (Q-07). Short UI or heading text: keep within the hint so the layout holds</t>
   </si>
   <si>
-    <t>U-122</t>
+    <t>U-128</t>
   </si>
   <si>
     <t>messages:form.optional</t>
@@ -4847,7 +4901,7 @@
     <t>Optional</t>
   </si>
   <si>
-    <t>U-123</t>
+    <t>U-129</t>
   </si>
   <si>
     <t>messages:form.submit</t>
@@ -4856,7 +4910,7 @@
     <t>Send inquiry</t>
   </si>
   <si>
-    <t>U-124</t>
+    <t>U-130</t>
   </si>
   <si>
     <t>messages:form.sending</t>
@@ -4865,7 +4919,7 @@
     <t>Sending…</t>
   </si>
   <si>
-    <t>U-125</t>
+    <t>U-131</t>
   </si>
   <si>
     <t>messages:form.errors.summary</t>
@@ -4874,7 +4928,7 @@
     <t>Please correct {count, plural, one {# field} other {# fields}} below.</t>
   </si>
   <si>
-    <t>U-126</t>
+    <t>U-132</t>
   </si>
   <si>
     <t>messages:form.errors.required</t>
@@ -4883,7 +4937,7 @@
     <t>This field is required.</t>
   </si>
   <si>
-    <t>U-127</t>
+    <t>U-133</t>
   </si>
   <si>
     <t>messages:form.errors.nameLength</t>
@@ -4892,7 +4946,7 @@
     <t>Enter between 2 and 100 characters.</t>
   </si>
   <si>
-    <t>U-128</t>
+    <t>U-134</t>
   </si>
   <si>
     <t>messages:form.errors.companyLength</t>
@@ -4901,7 +4955,7 @@
     <t>Enter up to 120 characters.</t>
   </si>
   <si>
-    <t>U-129</t>
+    <t>U-135</t>
   </si>
   <si>
     <t>messages:form.errors.email</t>
@@ -4910,7 +4964,7 @@
     <t>Enter a valid email address.</t>
   </si>
   <si>
-    <t>U-130</t>
+    <t>U-136</t>
   </si>
   <si>
     <t>messages:form.errors.phone</t>
@@ -4919,7 +4973,7 @@
     <t>Use digits, spaces or dashes, with an optional leading +.</t>
   </si>
   <si>
-    <t>U-131</t>
+    <t>U-137</t>
   </si>
   <si>
     <t>messages:form.errors.messageLength</t>
@@ -4928,7 +4982,7 @@
     <t>Enter between 10 and 3,000 characters.</t>
   </si>
   <si>
-    <t>U-132</t>
+    <t>U-138</t>
   </si>
   <si>
     <t>messages:form.errors.messageLinks</t>
@@ -4937,7 +4991,7 @@
     <t>Please include no more than 3 links.</t>
   </si>
   <si>
-    <t>U-133</t>
+    <t>U-139</t>
   </si>
   <si>
     <t>messages:form.errors.consent</t>
@@ -4946,7 +5000,7 @@
     <t>Please confirm before sending.</t>
   </si>
   <si>
-    <t>U-134</t>
+    <t>U-140</t>
   </si>
   <si>
     <t>messages:form.errors.verification</t>
@@ -4955,7 +5009,7 @@
     <t>We couldn’t verify the submission. Please try again.</t>
   </si>
   <si>
-    <t>U-135</t>
+    <t>U-141</t>
   </si>
   <si>
     <t>messages:form.errors.rateLimited</t>
@@ -4964,7 +5018,7 @@
     <t>Too many inquiries were sent from this connection. Please try again later, or contact us by email or phone.</t>
   </si>
   <si>
-    <t>U-136</t>
+    <t>U-142</t>
   </si>
   <si>
     <t>messages:form.errors.network</t>
@@ -4973,7 +5027,7 @@
     <t>We couldn’t send your inquiry. Your message is still here — please try again, or contact us by email or phone.</t>
   </si>
   <si>
-    <t>U-137</t>
+    <t>U-143</t>
   </si>
   <si>
     <t>messages:form.success.title</t>
@@ -4982,7 +5036,7 @@
     <t>Thank you — we’ve received your inquiry.</t>
   </si>
   <si>
-    <t>U-138</t>
+    <t>U-144</t>
   </si>
   <si>
     <t>messages:form.success.reference</t>
@@ -4991,7 +5045,7 @@
     <t>Reference: {ref}</t>
   </si>
   <si>
-    <t>U-139</t>
+    <t>U-145</t>
   </si>
   <si>
     <t>messages:form.success.next</t>
@@ -5000,7 +5054,7 @@
     <t>Our team will review it and reply by email.</t>
   </si>
   <si>
-    <t>U-140</t>
+    <t>U-146</t>
   </si>
   <si>
     <t>messages:form.success.contacts</t>
@@ -5009,7 +5063,7 @@
     <t>For anything urgent, contact our offices directly.</t>
   </si>
   <si>
-    <t>U-141</t>
+    <t>U-147</t>
   </si>
   <si>
     <t>messages:form.noscript</t>
@@ -5018,7 +5072,7 @@
     <t>This form needs JavaScript. You can also contact us directly:</t>
   </si>
   <si>
-    <t>U-142</t>
+    <t>U-148</t>
   </si>
   <si>
     <t>messages:contact.address</t>
@@ -5027,7 +5081,7 @@
     <t>Address</t>
   </si>
   <si>
-    <t>U-143</t>
+    <t>U-149</t>
   </si>
   <si>
     <t>messages:contact.hours</t>
@@ -5036,7 +5090,7 @@
     <t>Business hours</t>
   </si>
   <si>
-    <t>U-144</t>
+    <t>U-150</t>
   </si>
   <si>
     <t>messages:contact.getDirections</t>
@@ -5045,7 +5099,7 @@
     <t>Get directions</t>
   </si>
   <si>
-    <t>U-145</t>
+    <t>U-151</t>
   </si>
   <si>
     <t>messages:contact.loadMap</t>
@@ -5054,7 +5108,7 @@
     <t>Load map</t>
   </si>
   <si>
-    <t>U-146</t>
+    <t>U-152</t>
   </si>
   <si>
     <t>messages:contact.mapNotice</t>
@@ -5063,7 +5117,7 @@
     <t>The map is provided by Google Maps and loads only when you choose.</t>
   </si>
   <si>
-    <t>U-147</t>
+    <t>U-153</t>
   </si>
   <si>
     <t>messages:companyProfile.load</t>
@@ -5072,7 +5126,7 @@
     <t>Load presentation</t>
   </si>
   <si>
-    <t>U-148</t>
+    <t>U-154</t>
   </si>
   <si>
     <t>messages:companyProfile.loadNotice</t>
@@ -5081,7 +5135,7 @@
     <t>The presentation is hosted by Canva and loads only when you choose.</t>
   </si>
   <si>
-    <t>U-149</t>
+    <t>U-155</t>
   </si>
   <si>
     <t>messages:companyProfile.download</t>
@@ -5090,7 +5144,7 @@
     <t>Download PDF</t>
   </si>
   <si>
-    <t>U-150</t>
+    <t>U-156</t>
   </si>
   <si>
     <t>messages:companyProfile.fallback</t>
@@ -5099,13 +5153,13 @@
     <t>If the presentation doesn’t load, contact us for a copy.</t>
   </si>
   <si>
-    <t>U-151</t>
+    <t>U-157</t>
   </si>
   <si>
     <t>messages:notFound.title</t>
   </si>
   <si>
-    <t>U-152</t>
+    <t>U-158</t>
   </si>
   <si>
     <t>messages:notFound.body</t>
@@ -5114,7 +5168,7 @@
     <t>The page you’re looking for doesn’t exist or has moved.</t>
   </si>
   <si>
-    <t>U-153</t>
+    <t>U-159</t>
   </si>
   <si>
     <t>messages:notFound.home</t>
@@ -5123,7 +5177,7 @@
     <t>Go to the homepage</t>
   </si>
   <si>
-    <t>U-154</t>
+    <t>U-160</t>
   </si>
   <si>
     <t>messages:notFound.links</t>
@@ -5132,7 +5186,7 @@
     <t>Popular sections</t>
   </si>
   <si>
-    <t>U-155</t>
+    <t>U-161</t>
   </si>
   <si>
     <t>messages:legal.contents</t>
@@ -5141,7 +5195,7 @@
     <t>Contents</t>
   </si>
   <si>
-    <t>U-156</t>
+    <t>U-162</t>
   </si>
   <si>
     <t>messages:pending.category</t>
@@ -5150,7 +5204,7 @@
     <t>Category description — pending client (D-09)</t>
   </si>
   <si>
-    <t>U-157</t>
+    <t>U-163</t>
   </si>
   <si>
     <t>messages:pending.privacy</t>
@@ -5159,7 +5213,7 @@
     <t>Privacy policy text — pending client (D-16)</t>
   </si>
   <si>
-    <t>U-158</t>
+    <t>U-164</t>
   </si>
   <si>
     <t>messages:pending.companyProfile</t>
@@ -5168,7 +5222,7 @@
     <t>Company profile presentation — pending client (D-06)</t>
   </si>
   <si>
-    <t>U-159</t>
+    <t>U-165</t>
   </si>
   <si>
     <t>messages:pending.map</t>
@@ -15537,15 +15591,15 @@
         <v>1248</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
@@ -15562,26 +15616,26 @@
         <v>558</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>729</v>
+        <v>1251</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1208</v>
@@ -15590,18 +15644,18 @@
         <v>558</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1253</v>
+        <v>729</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
@@ -15621,15 +15675,15 @@
         <v>1256</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
@@ -15657,7 +15711,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -15677,15 +15731,15 @@
         <v>1262</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -15702,13 +15756,13 @@
         <v>558</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>744</v>
+        <v>1265</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -15718,10 +15772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1208</v>
@@ -15730,13 +15784,13 @@
         <v>558</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1267</v>
+        <v>744</v>
       </c>
       <c r="F22">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -15761,10 +15815,10 @@
         <v>1270</v>
       </c>
       <c r="F23">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -15789,10 +15843,10 @@
         <v>1273</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -15817,10 +15871,10 @@
         <v>1276</v>
       </c>
       <c r="F25">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -15845,10 +15899,10 @@
         <v>1279</v>
       </c>
       <c r="F26">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -15901,10 +15955,10 @@
         <v>1285</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G28">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -15929,10 +15983,10 @@
         <v>1288</v>
       </c>
       <c r="F29">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="G29">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -15957,10 +16011,10 @@
         <v>1291</v>
       </c>
       <c r="F30">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -15985,10 +16039,10 @@
         <v>1294</v>
       </c>
       <c r="F31">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -16013,10 +16067,10 @@
         <v>1297</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -16041,10 +16095,10 @@
         <v>1300</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G33">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -16069,10 +16123,10 @@
         <v>1303</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G34">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -16097,15 +16151,15 @@
         <v>1306</v>
       </c>
       <c r="F35">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G35">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -16125,15 +16179,15 @@
         <v>1309</v>
       </c>
       <c r="F36">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G36">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -16153,15 +16207,15 @@
         <v>1312</v>
       </c>
       <c r="F37">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G37">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -16181,15 +16235,15 @@
         <v>1315</v>
       </c>
       <c r="F38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -16209,10 +16263,10 @@
         <v>1318</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G39">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -16265,10 +16319,10 @@
         <v>1324</v>
       </c>
       <c r="F41">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -16293,10 +16347,10 @@
         <v>1327</v>
       </c>
       <c r="F42">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G42">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -16321,10 +16375,10 @@
         <v>1330</v>
       </c>
       <c r="F43">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -16349,10 +16403,10 @@
         <v>1333</v>
       </c>
       <c r="F44">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G44">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -16377,10 +16431,10 @@
         <v>1336</v>
       </c>
       <c r="F45">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G45">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -16405,15 +16459,15 @@
         <v>1339</v>
       </c>
       <c r="F46">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G46">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47">
@@ -16433,15 +16487,15 @@
         <v>1342</v>
       </c>
       <c r="F47">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
@@ -16461,23 +16515,23 @@
         <v>1345</v>
       </c>
       <c r="F48">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>1347</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>1348</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>1208</v>
@@ -16486,18 +16540,18 @@
         <v>558</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F49">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="50">
@@ -16545,23 +16599,23 @@
         <v>1355</v>
       </c>
       <c r="F51">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G51">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>1356</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>1357</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>1358</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>1208</v>
@@ -16570,18 +16624,18 @@
         <v>558</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F52">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="G52">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>53</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="53">
@@ -16601,10 +16655,10 @@
         <v>1362</v>
       </c>
       <c r="F53">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G53">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -16629,10 +16683,10 @@
         <v>1365</v>
       </c>
       <c r="F54">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G54">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -16685,10 +16739,10 @@
         <v>1371</v>
       </c>
       <c r="F56">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G56">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -16713,10 +16767,10 @@
         <v>1374</v>
       </c>
       <c r="F57">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="G57">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -16741,10 +16795,10 @@
         <v>1377</v>
       </c>
       <c r="F58">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="G58">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -16769,10 +16823,10 @@
         <v>1380</v>
       </c>
       <c r="F59">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="G59">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -16797,10 +16851,10 @@
         <v>1383</v>
       </c>
       <c r="F60">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="G60">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -16825,10 +16879,10 @@
         <v>1386</v>
       </c>
       <c r="F61">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G61">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -16853,15 +16907,15 @@
         <v>1389</v>
       </c>
       <c r="F62">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63">
@@ -16881,10 +16935,10 @@
         <v>1392</v>
       </c>
       <c r="F63">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="G63">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -16909,10 +16963,10 @@
         <v>1395</v>
       </c>
       <c r="F64">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G64">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -16937,10 +16991,10 @@
         <v>1398</v>
       </c>
       <c r="F65">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="G65">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -16965,10 +17019,10 @@
         <v>1401</v>
       </c>
       <c r="F66">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="G66">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
@@ -16993,10 +17047,10 @@
         <v>1404</v>
       </c>
       <c r="F67">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="G67">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
@@ -17021,15 +17075,15 @@
         <v>1407</v>
       </c>
       <c r="F68">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="69">
@@ -17049,10 +17103,10 @@
         <v>1410</v>
       </c>
       <c r="F69">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G69">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
@@ -17077,10 +17131,10 @@
         <v>1413</v>
       </c>
       <c r="F70">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
@@ -17105,10 +17159,10 @@
         <v>1416</v>
       </c>
       <c r="F71">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G71">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
@@ -17133,10 +17187,10 @@
         <v>1419</v>
       </c>
       <c r="F72">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="G72">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
@@ -17161,10 +17215,10 @@
         <v>1422</v>
       </c>
       <c r="F73">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="G73">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
@@ -17189,15 +17243,15 @@
         <v>1425</v>
       </c>
       <c r="F74">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G74">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75">
@@ -17217,15 +17271,15 @@
         <v>1428</v>
       </c>
       <c r="F75">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G75">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76">
@@ -17245,15 +17299,15 @@
         <v>1431</v>
       </c>
       <c r="F76">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G76">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77">
@@ -17273,10 +17327,10 @@
         <v>1434</v>
       </c>
       <c r="F77">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G77">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
@@ -17301,10 +17355,10 @@
         <v>1437</v>
       </c>
       <c r="F78">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G78">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
@@ -17329,10 +17383,10 @@
         <v>1440</v>
       </c>
       <c r="F79">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G79">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
@@ -17357,15 +17411,15 @@
         <v>1443</v>
       </c>
       <c r="F80">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
       <c r="J80" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="81">
@@ -17385,15 +17439,15 @@
         <v>1446</v>
       </c>
       <c r="F81">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G81">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
       <c r="J81" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="82">
@@ -17413,15 +17467,15 @@
         <v>1449</v>
       </c>
       <c r="F82">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G82">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="83">
@@ -17441,10 +17495,10 @@
         <v>1452</v>
       </c>
       <c r="F83">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G83">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
@@ -17469,10 +17523,10 @@
         <v>1455</v>
       </c>
       <c r="F84">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G84">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
@@ -17497,10 +17551,10 @@
         <v>1458</v>
       </c>
       <c r="F85">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G85">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
@@ -17525,10 +17579,10 @@
         <v>1461</v>
       </c>
       <c r="F86">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
@@ -17553,10 +17607,10 @@
         <v>1464</v>
       </c>
       <c r="F87">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G87">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
@@ -17581,10 +17635,10 @@
         <v>1467</v>
       </c>
       <c r="F88">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G88">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
@@ -17609,10 +17663,10 @@
         <v>1470</v>
       </c>
       <c r="F89">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G89">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
@@ -17637,15 +17691,15 @@
         <v>1473</v>
       </c>
       <c r="F90">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="G90">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91">
@@ -17665,10 +17719,10 @@
         <v>1476</v>
       </c>
       <c r="F91">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="G91">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
@@ -17693,10 +17747,10 @@
         <v>1479</v>
       </c>
       <c r="F92">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G92">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
@@ -17721,10 +17775,10 @@
         <v>1482</v>
       </c>
       <c r="F93">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G93">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
@@ -17749,10 +17803,10 @@
         <v>1485</v>
       </c>
       <c r="F94">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G94">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
@@ -17777,15 +17831,15 @@
         <v>1488</v>
       </c>
       <c r="F95">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G95">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96">
@@ -17805,15 +17859,15 @@
         <v>1491</v>
       </c>
       <c r="F96">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="G96">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="97">
@@ -17833,10 +17887,10 @@
         <v>1494</v>
       </c>
       <c r="F97">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G97">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
@@ -17861,10 +17915,10 @@
         <v>1497</v>
       </c>
       <c r="F98">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G98">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
@@ -17889,10 +17943,10 @@
         <v>1500</v>
       </c>
       <c r="F99">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G99">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
@@ -17917,10 +17971,10 @@
         <v>1503</v>
       </c>
       <c r="F100">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G100">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
@@ -17945,15 +17999,15 @@
         <v>1506</v>
       </c>
       <c r="F101">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G101">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
       <c r="J101" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="102">
@@ -17973,10 +18027,10 @@
         <v>1509</v>
       </c>
       <c r="F102">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G102">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
@@ -18001,10 +18055,10 @@
         <v>1512</v>
       </c>
       <c r="F103">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G103">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
@@ -18029,10 +18083,10 @@
         <v>1515</v>
       </c>
       <c r="F104">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G104">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
@@ -18057,10 +18111,10 @@
         <v>1518</v>
       </c>
       <c r="F105">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G105">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
@@ -18085,10 +18139,10 @@
         <v>1521</v>
       </c>
       <c r="F106">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G106">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
@@ -18113,10 +18167,10 @@
         <v>1524</v>
       </c>
       <c r="F107">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G107">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="3"/>
@@ -18141,15 +18195,15 @@
         <v>1527</v>
       </c>
       <c r="F108">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G108">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="3"/>
       <c r="J108" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="109">
@@ -18169,15 +18223,15 @@
         <v>1530</v>
       </c>
       <c r="F109">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G109">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="3"/>
       <c r="J109" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="110">
@@ -18197,10 +18251,10 @@
         <v>1533</v>
       </c>
       <c r="F110">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G110">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="3"/>
@@ -18250,13 +18304,13 @@
         <v>558</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>88</v>
+        <v>1539</v>
       </c>
       <c r="F112">
+        <v>12</v>
+      </c>
+      <c r="G112">
         <v>7</v>
-      </c>
-      <c r="G112">
-        <v>4</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="3"/>
@@ -18266,10 +18320,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>1208</v>
@@ -18278,13 +18332,13 @@
         <v>558</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>104</v>
+        <v>1542</v>
       </c>
       <c r="F113">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="G113">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="3"/>
@@ -18294,10 +18348,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>1208</v>
@@ -18306,7 +18360,7 @@
         <v>558</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="F114">
         <v>7</v>
@@ -18322,10 +18376,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>1208</v>
@@ -18334,26 +18388,26 @@
         <v>558</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="F115">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G115">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="3"/>
       <c r="J115" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>1208</v>
@@ -18362,13 +18416,13 @@
         <v>558</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="F116">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="G116">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="3"/>
@@ -18378,10 +18432,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>1208</v>
@@ -18390,13 +18444,13 @@
         <v>558</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="F117">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G117">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="3"/>
@@ -18406,10 +18460,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>1208</v>
@@ -18418,13 +18472,13 @@
         <v>558</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1555</v>
+        <v>88</v>
       </c>
       <c r="F118">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G118">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
@@ -18434,10 +18488,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>1208</v>
@@ -18446,13 +18500,13 @@
         <v>558</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1558</v>
+        <v>104</v>
       </c>
       <c r="F119">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G119">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="3"/>
@@ -18477,15 +18531,15 @@
         <v>1561</v>
       </c>
       <c r="F120">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G120">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="3"/>
       <c r="J120" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121">
@@ -18505,10 +18559,10 @@
         <v>1564</v>
       </c>
       <c r="F121">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="G121">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
@@ -18533,23 +18587,23 @@
         <v>1567</v>
       </c>
       <c r="F122">
-        <v>166</v>
+        <v>26</v>
       </c>
       <c r="G122">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
       <c r="J122" s="3" t="s">
-        <v>1568</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>1569</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>1570</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>1208</v>
@@ -18558,13 +18612,13 @@
         <v>558</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="F123">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G123">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H123" s="3"/>
       <c r="I123" s="3"/>
@@ -18574,10 +18628,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>1572</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>1573</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>1208</v>
@@ -18586,7 +18640,7 @@
         <v>558</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="F124">
         <v>16</v>
@@ -18602,10 +18656,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>1575</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>1576</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>1208</v>
@@ -18614,13 +18668,13 @@
         <v>558</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="F125">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G125">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H125" s="3"/>
       <c r="I125" s="3"/>
@@ -18630,10 +18684,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>1578</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>1579</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>1208</v>
@@ -18642,26 +18696,26 @@
         <v>558</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F126">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="G126">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H126" s="3"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>1581</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>1582</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>1208</v>
@@ -18670,13 +18724,13 @@
         <v>558</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F127">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="G127">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H127" s="3"/>
       <c r="I127" s="3"/>
@@ -18686,10 +18740,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>1584</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>1585</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>1208</v>
@@ -18698,18 +18752,18 @@
         <v>558</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F128">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="G128">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3" t="s">
-        <v>53</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="129">
@@ -18729,10 +18783,10 @@
         <v>1589</v>
       </c>
       <c r="F129">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G129">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H129" s="3"/>
       <c r="I129" s="3"/>
@@ -18757,10 +18811,10 @@
         <v>1592</v>
       </c>
       <c r="F130">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G130">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H130" s="3"/>
       <c r="I130" s="3"/>
@@ -18785,10 +18839,10 @@
         <v>1595</v>
       </c>
       <c r="F131">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="G131">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H131" s="3"/>
       <c r="I131" s="3"/>
@@ -18813,15 +18867,15 @@
         <v>1598</v>
       </c>
       <c r="F132">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G132">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="133">
@@ -18841,10 +18895,10 @@
         <v>1601</v>
       </c>
       <c r="F133">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G133">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
@@ -18869,10 +18923,10 @@
         <v>1604</v>
       </c>
       <c r="F134">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G134">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
@@ -18897,10 +18951,10 @@
         <v>1607</v>
       </c>
       <c r="F135">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="G135">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
@@ -18925,10 +18979,10 @@
         <v>1610</v>
       </c>
       <c r="F136">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="G136">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H136" s="3"/>
       <c r="I136" s="3"/>
@@ -18953,10 +19007,10 @@
         <v>1613</v>
       </c>
       <c r="F137">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="G137">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="3"/>
@@ -18981,10 +19035,10 @@
         <v>1616</v>
       </c>
       <c r="F138">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G138">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H138" s="3"/>
       <c r="I138" s="3"/>
@@ -19009,15 +19063,15 @@
         <v>1619</v>
       </c>
       <c r="F139">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G139">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H139" s="3"/>
       <c r="I139" s="3"/>
       <c r="J139" s="3" t="s">
-        <v>1346</v>
+        <v>53</v>
       </c>
     </row>
     <row r="140">
@@ -19037,10 +19091,10 @@
         <v>1622</v>
       </c>
       <c r="F140">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="G140">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H140" s="3"/>
       <c r="I140" s="3"/>
@@ -19065,10 +19119,10 @@
         <v>1625</v>
       </c>
       <c r="F141">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G141">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H141" s="3"/>
       <c r="I141" s="3"/>
@@ -19093,10 +19147,10 @@
         <v>1628</v>
       </c>
       <c r="F142">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G142">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="H142" s="3"/>
       <c r="I142" s="3"/>
@@ -19121,10 +19175,10 @@
         <v>1631</v>
       </c>
       <c r="F143">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="G143">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="H143" s="3"/>
       <c r="I143" s="3"/>
@@ -19149,10 +19203,10 @@
         <v>1634</v>
       </c>
       <c r="F144">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G144">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H144" s="3"/>
       <c r="I144" s="3"/>
@@ -19177,15 +19231,15 @@
         <v>1637</v>
       </c>
       <c r="F145">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G145">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H145" s="3"/>
       <c r="I145" s="3"/>
       <c r="J145" s="3" t="s">
-        <v>53</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="146">
@@ -19205,10 +19259,10 @@
         <v>1640</v>
       </c>
       <c r="F146">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="G146">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H146" s="3"/>
       <c r="I146" s="3"/>
@@ -19233,10 +19287,10 @@
         <v>1643</v>
       </c>
       <c r="F147">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="G147">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="H147" s="3"/>
       <c r="I147" s="3"/>
@@ -19261,10 +19315,10 @@
         <v>1646</v>
       </c>
       <c r="F148">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G148">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H148" s="3"/>
       <c r="I148" s="3"/>
@@ -19289,10 +19343,10 @@
         <v>1649</v>
       </c>
       <c r="F149">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="G149">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H149" s="3"/>
       <c r="I149" s="3"/>
@@ -19317,10 +19371,10 @@
         <v>1652</v>
       </c>
       <c r="F150">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G150">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
@@ -19345,10 +19399,10 @@
         <v>1655</v>
       </c>
       <c r="F151">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G151">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H151" s="3"/>
       <c r="I151" s="3"/>
@@ -19370,13 +19424,13 @@
         <v>558</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>756</v>
+        <v>1658</v>
       </c>
       <c r="F152">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G152">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
@@ -19386,10 +19440,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>1208</v>
@@ -19398,13 +19452,13 @@
         <v>558</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="F153">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G153">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H153" s="3"/>
       <c r="I153" s="3"/>
@@ -19414,10 +19468,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>1208</v>
@@ -19426,13 +19480,13 @@
         <v>558</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="F154">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G154">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H154" s="3"/>
       <c r="I154" s="3"/>
@@ -19442,10 +19496,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>1208</v>
@@ -19454,13 +19508,13 @@
         <v>558</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="F155">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="G155">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="H155" s="3"/>
       <c r="I155" s="3"/>
@@ -19470,10 +19524,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>1208</v>
@@ -19482,13 +19536,13 @@
         <v>558</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="F156">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G156">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
@@ -19498,10 +19552,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>1208</v>
@@ -19510,13 +19564,13 @@
         <v>558</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="F157">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G157">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H157" s="3"/>
       <c r="I157" s="3"/>
@@ -19526,10 +19580,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>1208</v>
@@ -19538,13 +19592,13 @@
         <v>558</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>1675</v>
+        <v>756</v>
       </c>
       <c r="F158">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G158">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H158" s="3"/>
       <c r="I158" s="3"/>
@@ -19569,10 +19623,10 @@
         <v>1678</v>
       </c>
       <c r="F159">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G159">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H159" s="3"/>
       <c r="I159" s="3"/>
@@ -19597,14 +19651,182 @@
         <v>1681</v>
       </c>
       <c r="F160">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G160">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H160" s="3"/>
       <c r="I160" s="3"/>
       <c r="J160" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F161">
+        <v>21</v>
+      </c>
+      <c r="G161">
+        <v>12</v>
+      </c>
+      <c r="H161" s="3"/>
+      <c r="I161" s="3"/>
+      <c r="J161" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F162">
+        <v>11</v>
+      </c>
+      <c r="G162">
+        <v>6</v>
+      </c>
+      <c r="H162" s="3"/>
+      <c r="I162" s="3"/>
+      <c r="J162" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F163">
+        <v>58</v>
+      </c>
+      <c r="G163">
+        <v>31</v>
+      </c>
+      <c r="H163" s="3"/>
+      <c r="I163" s="3"/>
+      <c r="J163" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F164">
+        <v>56</v>
+      </c>
+      <c r="G164">
+        <v>31</v>
+      </c>
+      <c r="H164" s="3"/>
+      <c r="I164" s="3"/>
+      <c r="J164" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="F165">
+        <v>68</v>
+      </c>
+      <c r="G165">
+        <v>37</v>
+      </c>
+      <c r="H165" s="3"/>
+      <c r="I165" s="3"/>
+      <c r="J165" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F166">
+        <v>36</v>
+      </c>
+      <c r="G166">
+        <v>19</v>
+      </c>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+      <c r="J166" s="3" t="s">
         <v>53</v>
       </c>
     </row>
@@ -19623,10 +19845,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>1682</v>
+        <v>1700</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1683</v>
+        <v>1701</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>27</v>
@@ -19640,31 +19862,31 @@
         <v>474</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1684</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1685</v>
+        <v>1703</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1686</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1687</v>
+        <v>1705</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1688</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1689</v>
+        <v>1707</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1690</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="6">
@@ -19672,7 +19894,7 @@
         <v>307</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1691</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="7">
@@ -19680,23 +19902,23 @@
         <v>282</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1691</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1692</v>
+        <v>1710</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1691</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1693</v>
+        <v>1711</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1694</v>
+        <v>1712</v>
       </c>
     </row>
   </sheetData>
